--- a/data/labels/v1/irr_adjudication_sheet.xlsx
+++ b/data/labels/v1/irr_adjudication_sheet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,2190 @@
           <t>adjudication_note</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>b7ab56f4c58361b6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>018d846d170a631b</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>018d846d170a631b</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>26c16e94dab6c75e</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Our high-performance enterprise class SSD include high-performance flash-based SSD and software solutions that are optimized for performance applications providing a range of capacity and performance levels primarily for use in enterprise servers and supporting high-volume online transactions, AI-related workloads, data analysis and other enterprise applications.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>106040</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2024/QTR3/20240820_10-K_edgar_data_106040_0000106040-24-000031.txt</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>A_vs_I</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>A-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>45bd86334b5a4e72</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>40bde3bec3a3f3b9</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>40bde3bec3a3f3b9</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>66956e3fc78f9b03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>We are in the early stages of implementing our plan for the construction and operation of clean-energy-powered data centers to lease to large enterprise information technology (IT) customers that are creating or addressing the growing demand for AI, Cloud and High-Performance Computing (HPC) digital services.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1174891</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2024/QTR2/20240409_10-K_edgar_data_1174891_0001493152-24-014061.txt</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>A_vs_I</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>060535d5cb5631a3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4144f4d0f5d5a037</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4144f4d0f5d5a037</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>c4e09d07456063ba</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>We continue to build and integrate AI into our offerings, and this innovation presents risks and challenges that could affect its adoption, and therefore our business.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1374339</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2024/QTR2/20240401_10-K_edgar_data_1374339_0001558370-24-004532.txt</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A-&gt;S</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>e2ccdb6ff8c9cbbc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4a98a4e32ca195a3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4a98a4e32ca195a3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5a52a717d1e3d7b4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The Hennessy Stance ESG ETF seeks long term growth of capital by combining environmental, social, and governance ESG and machine learning/artificial intelligence ML/AI in an ETF structure.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1145255</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2024/QTR4/20241211_10-K_edgar_data_1145255_0001437749-24-037244.txt</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A-&gt;S</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8b17e3468ddc4cfe</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>77342759203bcd77</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>77342759203bcd77</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6489b2d76fe80847</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>This Infrastructure-as-a-Service (IaaS) enables use cases including backups, multi-cloud, application storage, ransomware protection, and storage for AI/ML workflows.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1462056</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2024/QTR2/20240401_10-K_edgar_data_1462056_0001462056-24-000033.txt</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A-&gt;S</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cec8ccd31f1c7e24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9ff3a54dcf4d9d8a</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9ff3a54dcf4d9d8a</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bd2238fbee89c539</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Additionally, we deliver a range of connectivity solutions for the Internet of Things, smartphones, tablet computers, virtual reality and artificial intelligence/machine learning applications to help our customers meet their current challenges and future innovations.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1385157</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2024/QTR4/20241112_10-K_edgar_data_1385157_0001558370-24-015227.txt</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>A_vs_I</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00e4a2604a0468ec</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>b5c8399bb55eccda</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>b5c8399bb55eccda</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6f14a124157d5bf1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>We have entered into a Loan Agreement with Beyebe AI pursuant to which we may borrow up to 1,000,000 to fund our operations.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2016167</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2024/QTR4/20241227_10-K_edgar_data_2016167_0001753926-24-002159.txt</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>A_vs_I</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cc12d57c8ccc862b</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>daaa2b2c419e2496</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>daaa2b2c419e2496</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>97d63e6c8eea2dc9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>We are making investments in AI initiatives, including generative AI, to, among other things, recommend relevant unconnected content across our products, enhance our advertising tools, develop new products, and develop new features for existing products.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1326205</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2024/QTR2/20240624_10-K_edgar_data_1326205_0001185185-24-000650.txt</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A-&gt;S</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5d0bf3a1db9eadc5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>e2df4d3a834cff5f</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>e2df4d3a834cff5f</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5b47bcbd1929603c</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>This cloud-based AI-driven security operations platform for the modern SOC harnesses the power of AI to radically improve security outcomes and transform security operations.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1327567</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2024/QTR3/20240906_10-K_edgar_data_1327567_0001327567-24-000029.txt</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A_vs_I</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1319a1fdf61b9e7f</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>e8670325d27532fe</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>e8670325d27532fe</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ecefa070a45e4e23</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>We have invested and expect to continue to invest heavily in research and development for new and innovative products, including AI solutions.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1616533</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2024/QTR4/20241024_10-K_edgar_data_1616533_0001628280-24-043646.txt</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A-&gt;S</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>b162d7cf2e386f7e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>f233cfa1e8291d6d</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>f233cfa1e8291d6d</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2681119ba1f2fb80</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>In addition, Dow Jones produces customized Due Diligence Reports to assist its customers with regulatory compliance, including IntegrityCheck, a generative AI-enabled automated report.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1564708</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2024/QTR3/20240813_10-K_edgar_data_1564708_0001564708-24-000408.txt</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>A_vs_I</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aa93d9529c08a614</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fd676d1f8031506f</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fd676d1f8031506f</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>dbf16dd1158358fd</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>From February 2021 to April 2022, Benjamin has served as Senior Capital Market Advisor for Iveda Solutions, Inc. (NASDAQ: IVDA), an AI and IoT technology company to assist with financing and uplisting to Nasdaq.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1066764</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2024/QTR2/20240401_10-K_edgar_data_1066764_0001493152-24-012444.txt</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>A_vs_I</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>a07133e18416473b</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>49fac59fad5624d3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>49fac59fad5624d3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00b7f669d50a2cec</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>These clients are consciously evaluating potential areas where AI-enabled technologies could be utilized in the future.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1720420</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2024/QTR3/20240912_10-K_edgar_data_1720420_0001720420-24-000042.txt</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>I_vs_S</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>S-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>73b21526e0018334</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6687ff9d0220c3c1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6687ff9d0220c3c1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>273dee4547765cb6</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Additionally, accelerating AI trends could catalyze the smartphone transformation with incremental content driving unprecedented functional and physical densities.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2024/QTR4/20241115_10-K_edgar_data_4127_0000004127-24-000131.txt</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>I_vs_S</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>S-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>f7a9d8ed21ba97ab</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6c457c2fff577088</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6c457c2fff577088</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7f149b24b4a063a6</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>We plan to build Earth-2, a digital twin of the Earth on NVIDIA AI and NVIDIA Omniverse platforms.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1045810</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2024/QTR1/20240221_10-K_edgar_data_1045810_0001045810-24-000029.txt</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>I_vs_S</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>S-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>8e50645be7ce70dc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>78396ddc85221989</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>78396ddc85221989</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7598cdd1dc7647ff</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Advancements in technology, such as advanced safety systems; automated package sorting, handling, and delivery; autonomous delivery; third-party supply chain insight and management; artificial intelligence; vehicle platooning; alternative fuel vehicles; and digitization of freight services, may necessitate that we increase investments in order to remain competitive, and our customers may not be willing to accept higher rates to cover the cost of these investments.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1048911</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2024/QTR3/20240715_10-K_edgar_data_1048911_0000950170-24-083577.txt</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>I_vs_S</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>S-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>a37a2f892132db1b</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7c3bc0ff7f98b447</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7c3bc0ff7f98b447</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>e574f720ec83c9a4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Here are some of the technologies that we intend successfully to implement in our mobile application (during 1-18 months): Improvement of the implemented AI technology: The app will provide Implemented AI technology that is in the process of being fully implemented, revision and will undergo continuous refinement and improvement to ensure the highest level of performance.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1978111</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2024/QTR4/20241009_10-K_edgar_data_1978111_0001683168-24-007024.txt</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>S-&gt;A</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>b15fd04cb076182e</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>80cf4a6334cba61a</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>80cf4a6334cba61a</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5f33da566a302435</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>The ongoing development of AI and machine learning, algorithms, sensors, and flight control systems paves the way for fully autonomous eVTOL services in the future.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1481504</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2024/QTR4/20241008_10-K_edgar_data_1481504_0001477932-24-006252.txt</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>I_vs_S</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>S-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>c42e42dc5925e1ea</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>82b2d2b0d27928d2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>82b2d2b0d27928d2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>57077ab820d1730f</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dr. Bunting has other ongoing active business investments in the evolving internet artificial intelligence industry, as it relates to marketing and advertising.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1103795</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2024/QTR2/20240409_10-K_edgar_data_1103795_0001683168-24-002236.txt</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>S-&gt;A</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>30800c922b72d436</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8841c17407b5b230</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8841c17407b5b230</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>012872fb0537f778</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>For example, we will continue to enhance certain of our machine learning models to improve our customer capture and segmentation capabilities.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1116132</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2024/QTR3/20240815_10-K_edgar_data_1116132_0001116132-24-000018.txt</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>S-&gt;A</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dec17455e80df4b8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>c1893bcf4fffa083</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>c1893bcf4fffa083</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5b5721dc9ba6a21e</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>The process continues by acquiring building data to analyze energy consumption to quickly identify savings (and hence, improved NOI) with intelligent machine learning.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1108645</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2024/QTR2/20240401_10-K_edgar_data_1108645_0001477932-24-001631.txt</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>S-&gt;A</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0ab24d03c8239142</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>c76d591489724f5f</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>c76d591489724f5f</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>04c7039933b959aa</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Additionally, the proliferation of generative AI applications is expected to accelerate the creation of digital content such as text, images and video over the long-term.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1137789</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2024/QTR3/20240802_10-K_edgar_data_1137789_0001137789-24-000068.txt</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>I_vs_S</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>S-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>02578338add32948</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>df42379864a36f3b</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>df42379864a36f3b</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2387103833acfbe8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>In the future, we directly or through our third-party provided information technology systems or software may incorporate artificial intelligence AI capabilities into our business.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1052752</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2024/QTR1/20240215_10-K_edgar_data_1052752_0000950170-24-015982.txt</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>S-&gt;A</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>105f3b5a348c31a2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>e65f490dbe214fd0</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>e65f490dbe214fd0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>98c50baf6f6271ea</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Plan of Operation We devote substantial efforts to enter into new-emerging application industries of Internet Technology, Artificial Intelligence (AI) and the Internet of Things (IOT).</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1438461</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2024/QTR3/20240715_10-K_edgar_data_1438461_0001640334-24-001102.txt</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>S-&gt;A</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1a074f393fc0c04a</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>f106467bc3b0f7bc</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>f106467bc3b0f7bc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3f1206a26b863eeb</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>We believe that one of the most significant drivers of longer-term wearable display market adoption that will change the future of computing and result in broad adoption of AR in smaller wearable packages will be the augmentation of the real world with cloud-based information and AI.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1463972</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2024/QTR2/20240415_10-K_edgar_data_1463972_0001558370-24-005117.txt</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>I_vs_S</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>S-&gt;I</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>887b5b7b3f92667d</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>966d3309fbe43b6f</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>966d3309fbe43b6f</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0bd4675009165f2d</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>XENE Acquisition On February 7, 2024, SG DevCorp closed its acquisition of Majestic World Holdings, a real estate technology firm and owner of the Xene AI Software platform XENE Platform .</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1023994</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2024/QTR2/20240507_10-K_edgar_data_1023994_0001213900-24-040541.txt</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Manuf</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>A_vs_S</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A-&gt;S</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/labels/v1/irr_adjudication_sheet.xlsx
+++ b/data/labels/v1/irr_adjudication_sheet.xlsx
@@ -601,7 +601,11 @@
           <t>A-&gt;I</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -685,7 +689,11 @@
           <t>A-&gt;I</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -769,7 +777,11 @@
           <t>A-&gt;S</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -853,7 +865,11 @@
           <t>A-&gt;S</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -937,7 +953,11 @@
           <t>A-&gt;S</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1021,7 +1041,11 @@
           <t>A-&gt;I</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1105,7 +1129,11 @@
           <t>A-&gt;I</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1189,7 +1217,11 @@
           <t>A-&gt;S</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1273,7 +1305,11 @@
           <t>A-&gt;I</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1357,7 +1393,11 @@
           <t>A-&gt;S</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1441,7 +1481,11 @@
           <t>A-&gt;I</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1525,7 +1569,11 @@
           <t>A-&gt;I</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1609,7 +1657,11 @@
           <t>S-&gt;I</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1693,7 +1745,11 @@
           <t>S-&gt;I</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1777,7 +1833,11 @@
           <t>S-&gt;I</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1861,7 +1921,11 @@
           <t>S-&gt;I</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1945,7 +2009,11 @@
           <t>S-&gt;A</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -2029,7 +2097,11 @@
           <t>S-&gt;I</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -2113,7 +2185,11 @@
           <t>S-&gt;A</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2197,7 +2273,11 @@
           <t>S-&gt;A</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -2281,7 +2361,11 @@
           <t>S-&gt;A</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2365,7 +2449,11 @@
           <t>S-&gt;I</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2449,7 +2537,11 @@
           <t>S-&gt;A</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2533,7 +2625,11 @@
           <t>S-&gt;A</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2617,7 +2713,11 @@
           <t>S-&gt;I</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2701,7 +2801,11 @@
           <t>A-&gt;S</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Actionable</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr"/>
     </row>
   </sheetData>
